--- a/data/cleaned/cleaned_swq_physical_parameter_manual_cpcb_rj_2021_2025.xlsx
+++ b/data/cleaned/cleaned_swq_physical_parameter_manual_cpcb_rj_2021_2025.xlsx
@@ -626,7 +626,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>12-02-2021 08:30</t>
+          <t>2021-12-02 08:30:00</t>
         </is>
       </c>
       <c r="T2" t="n">
@@ -721,7 +721,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>12-04-2021 08:30</t>
+          <t>2021-12-04 08:30:00</t>
         </is>
       </c>
       <c r="T3" t="n">
@@ -816,7 +816,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>16-06-2021 08:30</t>
+          <t>2021-06-16 08:30:00</t>
         </is>
       </c>
       <c r="T4" t="n">
@@ -911,7 +911,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>16-08-2021 08:30</t>
+          <t>2021-08-16 08:30:00</t>
         </is>
       </c>
       <c r="T5" t="n">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>14-10-2021 08:30</t>
+          <t>2021-10-14 08:30:00</t>
         </is>
       </c>
       <c r="T6" t="n">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>09-12-2021 08:30</t>
+          <t>2021-09-12 08:30:00</t>
         </is>
       </c>
       <c r="T7" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T8" t="inlineStr"/>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T9" t="inlineStr"/>
@@ -1382,7 +1382,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>18-01-2021 08:30</t>
+          <t>2021-01-18 08:30:00</t>
         </is>
       </c>
       <c r="T11" t="inlineStr"/>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>11-02-2021 08:30</t>
+          <t>2021-11-02 08:30:00</t>
         </is>
       </c>
       <c r="T12" t="inlineStr"/>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T13" t="inlineStr"/>
@@ -1754,7 +1754,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>13-01-2021 08:30</t>
+          <t>2021-01-13 08:30:00</t>
         </is>
       </c>
       <c r="T14" t="inlineStr"/>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T15" t="inlineStr"/>
@@ -1940,7 +1940,7 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T16" t="inlineStr"/>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>14-01-2021 08:30</t>
+          <t>2021-01-14 08:30:00</t>
         </is>
       </c>
       <c r="T17" t="inlineStr"/>
@@ -2126,7 +2126,7 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>12-02-2021 08:30</t>
+          <t>2021-12-02 08:30:00</t>
         </is>
       </c>
       <c r="T18" t="inlineStr"/>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>19-03-2021 08:30</t>
+          <t>2021-03-19 08:30:00</t>
         </is>
       </c>
       <c r="T19" t="inlineStr"/>
@@ -2312,7 +2312,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T20" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T21" t="n">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>29-10-2021 08:30</t>
+          <t>2021-10-29 08:30:00</t>
         </is>
       </c>
       <c r="T22" t="n">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T23" t="n">
@@ -2708,7 +2708,7 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>29-10-2021 08:30</t>
+          <t>2021-10-29 08:30:00</t>
         </is>
       </c>
       <c r="T24" t="n">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>15-04-2021 08:30</t>
+          <t>2021-04-15 08:30:00</t>
         </is>
       </c>
       <c r="T25" t="n">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>25-10-2021 08:30</t>
+          <t>2021-10-25 08:30:00</t>
         </is>
       </c>
       <c r="T26" t="n">
@@ -3005,7 +3005,7 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T27" t="n">
@@ -3104,7 +3104,7 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>29-10-2021 08:30</t>
+          <t>2021-10-29 08:30:00</t>
         </is>
       </c>
       <c r="T28" t="n">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T29" t="n">
@@ -3302,7 +3302,7 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>29-10-2021 08:30</t>
+          <t>2021-10-29 08:30:00</t>
         </is>
       </c>
       <c r="T30" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>12-04-2021 08:30</t>
+          <t>2021-12-04 08:30:00</t>
         </is>
       </c>
       <c r="T31" t="n">
@@ -3500,7 +3500,7 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>14-10-2021 08:30</t>
+          <t>2021-10-14 08:30:00</t>
         </is>
       </c>
       <c r="T32" t="n">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T33" t="n">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>26-10-2021 08:30</t>
+          <t>2021-10-26 08:30:00</t>
         </is>
       </c>
       <c r="T34" t="n">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T35" t="n">
@@ -3896,7 +3896,7 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>25-10-2021 08:30</t>
+          <t>2021-10-25 08:30:00</t>
         </is>
       </c>
       <c r="T36" t="n">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T37" t="n">
@@ -4094,7 +4094,7 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>11-10-2021 08:30</t>
+          <t>2021-11-10 08:30:00</t>
         </is>
       </c>
       <c r="T38" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T39" t="n">
@@ -4292,7 +4292,7 @@
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>11-10-2021 08:30</t>
+          <t>2021-11-10 08:30:00</t>
         </is>
       </c>
       <c r="T40" t="n">
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>12-04-2021 08:30</t>
+          <t>2021-12-04 08:30:00</t>
         </is>
       </c>
       <c r="T41" t="n">
@@ -4490,7 +4490,7 @@
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>14-10-2021 08:30</t>
+          <t>2021-10-14 08:30:00</t>
         </is>
       </c>
       <c r="T42" t="n">
@@ -4589,7 +4589,7 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T43" t="n">
@@ -4688,7 +4688,7 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>29-10-2021 08:30</t>
+          <t>2021-10-29 08:30:00</t>
         </is>
       </c>
       <c r="T44" t="n">
@@ -4787,7 +4787,7 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T45" t="n">
@@ -4886,7 +4886,7 @@
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>29-10-2021 08:30</t>
+          <t>2021-10-29 08:30:00</t>
         </is>
       </c>
       <c r="T46" t="n">
@@ -4985,7 +4985,7 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T47" t="n">
@@ -5084,7 +5084,7 @@
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>29-10-2021 08:30</t>
+          <t>2021-10-29 08:30:00</t>
         </is>
       </c>
       <c r="T48" t="n">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T49" t="n">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>29-10-2021 08:30</t>
+          <t>2021-10-29 08:30:00</t>
         </is>
       </c>
       <c r="T50" t="n">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T51" t="n">
@@ -5480,7 +5480,7 @@
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>11-10-2021 08:30</t>
+          <t>2021-11-10 08:30:00</t>
         </is>
       </c>
       <c r="T52" t="n">
@@ -5579,7 +5579,7 @@
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T53" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>27-10-2021 08:30</t>
+          <t>2021-10-27 08:30:00</t>
         </is>
       </c>
       <c r="T54" t="n">
@@ -5777,7 +5777,7 @@
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T55" t="n">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>29-10-2021 08:30</t>
+          <t>2021-10-29 08:30:00</t>
         </is>
       </c>
       <c r="T56" t="n">
@@ -5975,7 +5975,7 @@
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T57" t="n">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>29-10-2021 08:30</t>
+          <t>2021-10-29 08:30:00</t>
         </is>
       </c>
       <c r="T58" t="n">
@@ -6173,7 +6173,7 @@
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T59" t="n">
@@ -6272,7 +6272,7 @@
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>29-10-2021 08:30</t>
+          <t>2021-10-29 08:30:00</t>
         </is>
       </c>
       <c r="T60" t="n">
@@ -6371,7 +6371,7 @@
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>15-01-2021 08:30</t>
+          <t>2021-01-15 08:30:00</t>
         </is>
       </c>
       <c r="T61" t="inlineStr"/>
@@ -6464,7 +6464,7 @@
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T62" t="inlineStr"/>
@@ -6557,7 +6557,7 @@
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>06-03-2021 08:30</t>
+          <t>2021-06-03 08:30:00</t>
         </is>
       </c>
       <c r="T63" t="inlineStr"/>
@@ -6650,7 +6650,7 @@
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>22-01-2021 08:30</t>
+          <t>2021-01-22 08:30:00</t>
         </is>
       </c>
       <c r="T64" t="inlineStr"/>
@@ -6743,7 +6743,7 @@
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>22-02-2021 08:30</t>
+          <t>2021-02-22 08:30:00</t>
         </is>
       </c>
       <c r="T65" t="inlineStr"/>
@@ -6836,7 +6836,7 @@
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>19-03-2021 08:30</t>
+          <t>2021-03-19 08:30:00</t>
         </is>
       </c>
       <c r="T66" t="inlineStr"/>
@@ -6929,7 +6929,7 @@
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>22-02-2021 08:30</t>
+          <t>2021-02-22 08:30:00</t>
         </is>
       </c>
       <c r="T67" t="inlineStr"/>
@@ -7022,7 +7022,7 @@
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>15-01-2021 08:30</t>
+          <t>2021-01-15 08:30:00</t>
         </is>
       </c>
       <c r="T68" t="inlineStr"/>
@@ -7115,7 +7115,7 @@
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T69" t="inlineStr"/>
@@ -7208,7 +7208,7 @@
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T70" t="n">
@@ -7307,7 +7307,7 @@
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>27-10-2021 08:30</t>
+          <t>2021-10-27 08:30:00</t>
         </is>
       </c>
       <c r="T71" t="n">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>16-02-2021 08:30</t>
+          <t>2021-02-16 08:30:00</t>
         </is>
       </c>
       <c r="T72" t="inlineStr"/>
@@ -7499,7 +7499,7 @@
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>25-01-2021 08:30</t>
+          <t>2021-01-25 08:30:00</t>
         </is>
       </c>
       <c r="T73" t="inlineStr"/>
@@ -7592,7 +7592,7 @@
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>07-03-2021 08:30</t>
+          <t>2021-07-03 08:30:00</t>
         </is>
       </c>
       <c r="T74" t="inlineStr"/>
@@ -7685,7 +7685,7 @@
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>28-05-2021 08:30</t>
+          <t>2021-05-28 08:30:00</t>
         </is>
       </c>
       <c r="T75" t="n">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>12-10-2021 08:30</t>
+          <t>2021-12-10 08:30:00</t>
         </is>
       </c>
       <c r="T76" t="n">
@@ -7883,7 +7883,7 @@
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>07-04-2021 08:30</t>
+          <t>2021-07-04 08:30:00</t>
         </is>
       </c>
       <c r="T77" t="n">
@@ -7982,7 +7982,7 @@
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T78" t="n">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T79" t="n">
@@ -8180,7 +8180,7 @@
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>27-10-2021 08:30</t>
+          <t>2021-10-27 08:30:00</t>
         </is>
       </c>
       <c r="T80" t="n">
@@ -8279,7 +8279,7 @@
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>12-04-2021 08:30</t>
+          <t>2021-12-04 08:30:00</t>
         </is>
       </c>
       <c r="T81" t="n">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>15-10-2021 08:30</t>
+          <t>2021-10-15 08:30:00</t>
         </is>
       </c>
       <c r="T82" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>12-02-2021 08:30</t>
+          <t>2021-12-02 08:30:00</t>
         </is>
       </c>
       <c r="T83" t="n">
@@ -8572,7 +8572,7 @@
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>12-04-2021 08:30</t>
+          <t>2021-12-04 08:30:00</t>
         </is>
       </c>
       <c r="T84" t="n">
@@ -8667,7 +8667,7 @@
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>16-06-2021 08:30</t>
+          <t>2021-06-16 08:30:00</t>
         </is>
       </c>
       <c r="T85" t="n">
@@ -8762,7 +8762,7 @@
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>16-08-2021 08:30</t>
+          <t>2021-08-16 08:30:00</t>
         </is>
       </c>
       <c r="T86" t="n">
@@ -8857,7 +8857,7 @@
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>14-10-2021 08:30</t>
+          <t>2021-10-14 08:30:00</t>
         </is>
       </c>
       <c r="T87" t="n">
@@ -8952,7 +8952,7 @@
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>09-12-2021 08:30</t>
+          <t>2021-09-12 08:30:00</t>
         </is>
       </c>
       <c r="T88" t="n">
@@ -9047,7 +9047,7 @@
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>15-01-2021 08:30</t>
+          <t>2021-01-15 08:30:00</t>
         </is>
       </c>
       <c r="T89" t="inlineStr"/>
@@ -9140,7 +9140,7 @@
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>11-02-2021 08:30</t>
+          <t>2021-11-02 08:30:00</t>
         </is>
       </c>
       <c r="T90" t="inlineStr"/>
@@ -9233,7 +9233,7 @@
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T91" t="inlineStr"/>
@@ -9326,7 +9326,7 @@
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>15-01-2021 08:30</t>
+          <t>2021-01-15 08:30:00</t>
         </is>
       </c>
       <c r="T92" t="inlineStr"/>
@@ -9419,7 +9419,7 @@
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>11-02-2021 08:30</t>
+          <t>2021-11-02 08:30:00</t>
         </is>
       </c>
       <c r="T93" t="inlineStr"/>
@@ -9512,7 +9512,7 @@
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T94" t="inlineStr"/>
@@ -9605,7 +9605,7 @@
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>15-01-2021 08:30</t>
+          <t>2021-01-15 08:30:00</t>
         </is>
       </c>
       <c r="T95" t="inlineStr"/>
@@ -9698,7 +9698,7 @@
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>11-02-2021 08:30</t>
+          <t>2021-11-02 08:30:00</t>
         </is>
       </c>
       <c r="T96" t="inlineStr"/>
@@ -9791,7 +9791,7 @@
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T97" t="inlineStr"/>
@@ -9884,7 +9884,7 @@
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>09-01-2021 08:30</t>
+          <t>2021-09-01 08:30:00</t>
         </is>
       </c>
       <c r="T98" t="n">
@@ -9979,7 +9979,7 @@
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>07-02-2021 08:30</t>
+          <t>2021-07-02 08:30:00</t>
         </is>
       </c>
       <c r="T99" t="n">
@@ -10074,7 +10074,7 @@
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T100" t="n">
@@ -10169,7 +10169,7 @@
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T101" t="n">
@@ -10264,7 +10264,7 @@
       </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>03-06-2021 08:30</t>
+          <t>2021-03-06 08:30:00</t>
         </is>
       </c>
       <c r="T102" t="n">
@@ -10359,7 +10359,7 @@
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>07-07-2021 08:30</t>
+          <t>2021-07-07 08:30:00</t>
         </is>
       </c>
       <c r="T103" t="n">
@@ -10454,7 +10454,7 @@
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>10-08-2021 08:30</t>
+          <t>2021-10-08 08:30:00</t>
         </is>
       </c>
       <c r="T104" t="n">
@@ -10549,7 +10549,7 @@
       </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t>15-09-2021 08:30</t>
+          <t>2021-09-15 08:30:00</t>
         </is>
       </c>
       <c r="T105" t="n">
@@ -10644,7 +10644,7 @@
       </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>18-10-2021 08:30</t>
+          <t>2021-10-18 08:30:00</t>
         </is>
       </c>
       <c r="T106" t="n">
@@ -10739,7 +10739,7 @@
       </c>
       <c r="S107" t="inlineStr">
         <is>
-          <t>22-11-2021 08:30</t>
+          <t>2021-11-22 08:30:00</t>
         </is>
       </c>
       <c r="T107" t="n">
@@ -10834,7 +10834,7 @@
       </c>
       <c r="S108" t="inlineStr">
         <is>
-          <t>13-12-2021 08:30</t>
+          <t>2021-12-13 08:30:00</t>
         </is>
       </c>
       <c r="T108" t="n">
@@ -10929,7 +10929,7 @@
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>12-02-2021 08:30</t>
+          <t>2021-12-02 08:30:00</t>
         </is>
       </c>
       <c r="T109" t="n">
@@ -11024,7 +11024,7 @@
       </c>
       <c r="S110" t="inlineStr">
         <is>
-          <t>12-04-2021 08:30</t>
+          <t>2021-12-04 08:30:00</t>
         </is>
       </c>
       <c r="T110" t="n">
@@ -11119,7 +11119,7 @@
       </c>
       <c r="S111" t="inlineStr">
         <is>
-          <t>16-06-2021 08:30</t>
+          <t>2021-06-16 08:30:00</t>
         </is>
       </c>
       <c r="T111" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t>06-08-2021 08:30</t>
+          <t>2021-06-08 08:30:00</t>
         </is>
       </c>
       <c r="T112" t="n">
@@ -11309,7 +11309,7 @@
       </c>
       <c r="S113" t="inlineStr">
         <is>
-          <t>14-10-2021 08:30</t>
+          <t>2021-10-14 08:30:00</t>
         </is>
       </c>
       <c r="T113" t="n">
@@ -11404,7 +11404,7 @@
       </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t>09-12-2021 08:30</t>
+          <t>2021-09-12 08:30:00</t>
         </is>
       </c>
       <c r="T114" t="n">
@@ -11499,7 +11499,7 @@
       </c>
       <c r="S115" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T115" t="n">
@@ -11594,7 +11594,7 @@
       </c>
       <c r="S116" t="inlineStr">
         <is>
-          <t>12-02-2021 08:30</t>
+          <t>2021-12-02 08:30:00</t>
         </is>
       </c>
       <c r="T116" t="n">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="S117" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T117" t="n">
@@ -11784,7 +11784,7 @@
       </c>
       <c r="S118" t="inlineStr">
         <is>
-          <t>12-04-2021 08:30</t>
+          <t>2021-12-04 08:30:00</t>
         </is>
       </c>
       <c r="T118" t="n">
@@ -11879,7 +11879,7 @@
       </c>
       <c r="S119" t="inlineStr">
         <is>
-          <t>25-05-2021 08:30</t>
+          <t>2021-05-25 08:30:00</t>
         </is>
       </c>
       <c r="T119" t="n">
@@ -11974,7 +11974,7 @@
       </c>
       <c r="S120" t="inlineStr">
         <is>
-          <t>16-06-2021 08:30</t>
+          <t>2021-06-16 08:30:00</t>
         </is>
       </c>
       <c r="T120" t="n">
@@ -12069,7 +12069,7 @@
       </c>
       <c r="S121" t="inlineStr">
         <is>
-          <t>19-07-2021 08:30</t>
+          <t>2021-07-19 08:30:00</t>
         </is>
       </c>
       <c r="T121" t="n">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="S122" t="inlineStr">
         <is>
-          <t>16-08-2021 08:30</t>
+          <t>2021-08-16 08:30:00</t>
         </is>
       </c>
       <c r="T122" t="n">
@@ -12259,7 +12259,7 @@
       </c>
       <c r="S123" t="inlineStr">
         <is>
-          <t>08-09-2021 08:30</t>
+          <t>2021-08-09 08:30:00</t>
         </is>
       </c>
       <c r="T123" t="n">
@@ -12354,7 +12354,7 @@
       </c>
       <c r="S124" t="inlineStr">
         <is>
-          <t>14-10-2021 08:30</t>
+          <t>2021-10-14 08:30:00</t>
         </is>
       </c>
       <c r="T124" t="n">
@@ -12449,7 +12449,7 @@
       </c>
       <c r="S125" t="inlineStr">
         <is>
-          <t>11-11-2021 08:30</t>
+          <t>2021-11-11 08:30:00</t>
         </is>
       </c>
       <c r="T125" t="n">
@@ -12544,7 +12544,7 @@
       </c>
       <c r="S126" t="inlineStr">
         <is>
-          <t>09-12-2021 08:30</t>
+          <t>2021-09-12 08:30:00</t>
         </is>
       </c>
       <c r="T126" t="n">
@@ -12639,7 +12639,7 @@
       </c>
       <c r="S127" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T127" t="inlineStr"/>
@@ -12732,7 +12732,7 @@
       </c>
       <c r="S128" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T128" t="inlineStr"/>
@@ -12825,7 +12825,7 @@
       </c>
       <c r="S129" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T129" t="inlineStr"/>
@@ -12918,7 +12918,7 @@
       </c>
       <c r="S130" t="inlineStr">
         <is>
-          <t>04-04-2021 08:30</t>
+          <t>2021-04-04 08:30:00</t>
         </is>
       </c>
       <c r="T130" t="n">
@@ -13017,7 +13017,7 @@
       </c>
       <c r="S131" t="inlineStr">
         <is>
-          <t>11-10-2021 08:30</t>
+          <t>2021-11-10 08:30:00</t>
         </is>
       </c>
       <c r="T131" t="n">
@@ -13116,7 +13116,7 @@
       </c>
       <c r="S132" t="inlineStr">
         <is>
-          <t>04-04-2021 08:30</t>
+          <t>2021-04-04 08:30:00</t>
         </is>
       </c>
       <c r="T132" t="n">
@@ -13215,7 +13215,7 @@
       </c>
       <c r="S133" t="inlineStr">
         <is>
-          <t>11-10-2021 08:30</t>
+          <t>2021-11-10 08:30:00</t>
         </is>
       </c>
       <c r="T133" t="n">
@@ -13314,7 +13314,7 @@
       </c>
       <c r="S134" t="inlineStr">
         <is>
-          <t>15-04-2021 08:30</t>
+          <t>2021-04-15 08:30:00</t>
         </is>
       </c>
       <c r="T134" t="n">
@@ -13413,7 +13413,7 @@
       </c>
       <c r="S135" t="inlineStr">
         <is>
-          <t>11-10-2021 08:30</t>
+          <t>2021-11-10 08:30:00</t>
         </is>
       </c>
       <c r="T135" t="n">
@@ -13512,7 +13512,7 @@
       </c>
       <c r="S136" t="inlineStr">
         <is>
-          <t>28-05-2021 08:30</t>
+          <t>2021-05-28 08:30:00</t>
         </is>
       </c>
       <c r="T136" t="n">
@@ -13611,7 +13611,7 @@
       </c>
       <c r="S137" t="inlineStr">
         <is>
-          <t>26-10-2021 08:30</t>
+          <t>2021-10-26 08:30:00</t>
         </is>
       </c>
       <c r="T137" t="n">
@@ -13710,7 +13710,7 @@
       </c>
       <c r="S138" t="inlineStr">
         <is>
-          <t>27-05-2021 08:30</t>
+          <t>2021-05-27 08:30:00</t>
         </is>
       </c>
       <c r="T138" t="n">
@@ -13809,7 +13809,7 @@
       </c>
       <c r="S139" t="inlineStr">
         <is>
-          <t>28-10-2021 08:30</t>
+          <t>2021-10-28 08:30:00</t>
         </is>
       </c>
       <c r="T139" t="n">
@@ -13908,7 +13908,7 @@
       </c>
       <c r="S140" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T140" t="n">
@@ -14007,7 +14007,7 @@
       </c>
       <c r="S141" t="inlineStr">
         <is>
-          <t>27-10-2021 08:30</t>
+          <t>2021-10-27 08:30:00</t>
         </is>
       </c>
       <c r="T141" t="n">
@@ -14106,7 +14106,7 @@
       </c>
       <c r="S142" t="inlineStr">
         <is>
-          <t>10-04-2021 08:30</t>
+          <t>2021-10-04 08:30:00</t>
         </is>
       </c>
       <c r="T142" t="n">
@@ -14205,7 +14205,7 @@
       </c>
       <c r="S143" t="inlineStr">
         <is>
-          <t>14-10-2021 08:30</t>
+          <t>2021-10-14 08:30:00</t>
         </is>
       </c>
       <c r="T143" t="n">
@@ -14304,7 +14304,7 @@
       </c>
       <c r="S144" t="inlineStr">
         <is>
-          <t>31-05-2021 08:30</t>
+          <t>2021-05-31 08:30:00</t>
         </is>
       </c>
       <c r="T144" t="n">
@@ -14403,7 +14403,7 @@
       </c>
       <c r="S145" t="inlineStr">
         <is>
-          <t>26-10-2021 08:30</t>
+          <t>2021-10-26 08:30:00</t>
         </is>
       </c>
       <c r="T145" t="n">
@@ -14502,7 +14502,7 @@
       </c>
       <c r="S146" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T146" t="n">
@@ -14601,7 +14601,7 @@
       </c>
       <c r="S147" t="inlineStr">
         <is>
-          <t>27-10-2021 08:30</t>
+          <t>2021-10-27 08:30:00</t>
         </is>
       </c>
       <c r="T147" t="n">
@@ -14700,7 +14700,7 @@
       </c>
       <c r="S148" t="inlineStr">
         <is>
-          <t>15-04-2021 08:30</t>
+          <t>2021-04-15 08:30:00</t>
         </is>
       </c>
       <c r="T148" t="n">
@@ -14799,7 +14799,7 @@
       </c>
       <c r="S149" t="inlineStr">
         <is>
-          <t>11-10-2021 08:30</t>
+          <t>2021-11-10 08:30:00</t>
         </is>
       </c>
       <c r="T149" t="n">
@@ -14898,7 +14898,7 @@
       </c>
       <c r="S150" t="inlineStr">
         <is>
-          <t>12-04-2021 08:30</t>
+          <t>2021-12-04 08:30:00</t>
         </is>
       </c>
       <c r="T150" t="n">
@@ -14997,7 +14997,7 @@
       </c>
       <c r="S151" t="inlineStr">
         <is>
-          <t>14-10-2021 08:30</t>
+          <t>2021-10-14 08:30:00</t>
         </is>
       </c>
       <c r="T151" t="n">
@@ -15096,7 +15096,7 @@
       </c>
       <c r="S152" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T152" t="n">
@@ -15191,7 +15191,7 @@
       </c>
       <c r="S153" t="inlineStr">
         <is>
-          <t>10-06-2021 08:30</t>
+          <t>2021-10-06 08:30:00</t>
         </is>
       </c>
       <c r="T153" t="n">
@@ -15286,7 +15286,7 @@
       </c>
       <c r="S154" t="inlineStr">
         <is>
-          <t>16-09-2021 08:30</t>
+          <t>2021-09-16 08:30:00</t>
         </is>
       </c>
       <c r="T154" t="n">
@@ -15381,7 +15381,7 @@
       </c>
       <c r="S155" t="inlineStr">
         <is>
-          <t>23-11-2021 08:30</t>
+          <t>2021-11-23 08:30:00</t>
         </is>
       </c>
       <c r="T155" t="n">
@@ -15476,7 +15476,7 @@
       </c>
       <c r="S156" t="inlineStr">
         <is>
-          <t>09-01-2021 08:30</t>
+          <t>2021-09-01 08:30:00</t>
         </is>
       </c>
       <c r="T156" t="n">
@@ -15571,7 +15571,7 @@
       </c>
       <c r="S157" t="inlineStr">
         <is>
-          <t>07-02-2021 08:30</t>
+          <t>2021-07-02 08:30:00</t>
         </is>
       </c>
       <c r="T157" t="n">
@@ -15666,7 +15666,7 @@
       </c>
       <c r="S158" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T158" t="n">
@@ -15761,7 +15761,7 @@
       </c>
       <c r="S159" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T159" t="n">
@@ -15856,7 +15856,7 @@
       </c>
       <c r="S160" t="inlineStr">
         <is>
-          <t>03-06-2021 08:30</t>
+          <t>2021-03-06 08:30:00</t>
         </is>
       </c>
       <c r="T160" t="n">
@@ -15951,7 +15951,7 @@
       </c>
       <c r="S161" t="inlineStr">
         <is>
-          <t>07-07-2021 08:30</t>
+          <t>2021-07-07 08:30:00</t>
         </is>
       </c>
       <c r="T161" t="n">
@@ -16046,7 +16046,7 @@
       </c>
       <c r="S162" t="inlineStr">
         <is>
-          <t>10-08-2021 08:30</t>
+          <t>2021-10-08 08:30:00</t>
         </is>
       </c>
       <c r="T162" t="n">
@@ -16141,7 +16141,7 @@
       </c>
       <c r="S163" t="inlineStr">
         <is>
-          <t>15-09-2021 08:30</t>
+          <t>2021-09-15 08:30:00</t>
         </is>
       </c>
       <c r="T163" t="n">
@@ -16236,7 +16236,7 @@
       </c>
       <c r="S164" t="inlineStr">
         <is>
-          <t>18-10-2021 08:30</t>
+          <t>2021-10-18 08:30:00</t>
         </is>
       </c>
       <c r="T164" t="n">
@@ -16331,7 +16331,7 @@
       </c>
       <c r="S165" t="inlineStr">
         <is>
-          <t>22-11-2021 08:30</t>
+          <t>2021-11-22 08:30:00</t>
         </is>
       </c>
       <c r="T165" t="n">
@@ -16426,7 +16426,7 @@
       </c>
       <c r="S166" t="inlineStr">
         <is>
-          <t>13-12-2021 08:30</t>
+          <t>2021-12-13 08:30:00</t>
         </is>
       </c>
       <c r="T166" t="n">
@@ -16521,7 +16521,7 @@
       </c>
       <c r="S167" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T167" t="n">
@@ -16620,7 +16620,7 @@
       </c>
       <c r="S168" t="inlineStr">
         <is>
-          <t>26-10-2021 08:30</t>
+          <t>2021-10-26 08:30:00</t>
         </is>
       </c>
       <c r="T168" t="n">
@@ -16719,7 +16719,7 @@
       </c>
       <c r="S169" t="inlineStr">
         <is>
-          <t>17-08-2021 08:30</t>
+          <t>2021-08-17 08:30:00</t>
         </is>
       </c>
       <c r="T169" t="n">
@@ -16814,7 +16814,7 @@
       </c>
       <c r="S170" t="inlineStr">
         <is>
-          <t>24-10-2021 08:30</t>
+          <t>2021-10-24 08:30:00</t>
         </is>
       </c>
       <c r="T170" t="n">
@@ -16909,7 +16909,7 @@
       </c>
       <c r="S171" t="inlineStr">
         <is>
-          <t>12-02-2021 08:30</t>
+          <t>2021-12-02 08:30:00</t>
         </is>
       </c>
       <c r="T171" t="n">
@@ -17004,7 +17004,7 @@
       </c>
       <c r="S172" t="inlineStr">
         <is>
-          <t>12-04-2021 08:30</t>
+          <t>2021-12-04 08:30:00</t>
         </is>
       </c>
       <c r="T172" t="n">
@@ -17099,7 +17099,7 @@
       </c>
       <c r="S173" t="inlineStr">
         <is>
-          <t>16-06-2021 08:30</t>
+          <t>2021-06-16 08:30:00</t>
         </is>
       </c>
       <c r="T173" t="n">
@@ -17194,7 +17194,7 @@
       </c>
       <c r="S174" t="inlineStr">
         <is>
-          <t>16-08-2021 08:30</t>
+          <t>2021-08-16 08:30:00</t>
         </is>
       </c>
       <c r="T174" t="n">
@@ -17289,7 +17289,7 @@
       </c>
       <c r="S175" t="inlineStr">
         <is>
-          <t>14-10-2021 08:30</t>
+          <t>2021-10-14 08:30:00</t>
         </is>
       </c>
       <c r="T175" t="n">
@@ -17384,7 +17384,7 @@
       </c>
       <c r="S176" t="inlineStr">
         <is>
-          <t>09-12-2021 08:30</t>
+          <t>2021-09-12 08:30:00</t>
         </is>
       </c>
       <c r="T176" t="n">
@@ -17479,7 +17479,7 @@
       </c>
       <c r="S177" t="inlineStr">
         <is>
-          <t>12-02-2021 08:30</t>
+          <t>2021-12-02 08:30:00</t>
         </is>
       </c>
       <c r="T177" t="n">
@@ -17574,7 +17574,7 @@
       </c>
       <c r="S178" t="inlineStr">
         <is>
-          <t>12-04-2021 08:30</t>
+          <t>2021-12-04 08:30:00</t>
         </is>
       </c>
       <c r="T178" t="n">
@@ -17669,7 +17669,7 @@
       </c>
       <c r="S179" t="inlineStr">
         <is>
-          <t>16-06-2021 08:30</t>
+          <t>2021-06-16 08:30:00</t>
         </is>
       </c>
       <c r="T179" t="n">
@@ -17764,7 +17764,7 @@
       </c>
       <c r="S180" t="inlineStr">
         <is>
-          <t>16-08-2021 08:30</t>
+          <t>2021-08-16 08:30:00</t>
         </is>
       </c>
       <c r="T180" t="n">
@@ -17859,7 +17859,7 @@
       </c>
       <c r="S181" t="inlineStr">
         <is>
-          <t>14-10-2021 08:30</t>
+          <t>2021-10-14 08:30:00</t>
         </is>
       </c>
       <c r="T181" t="n">
@@ -17954,7 +17954,7 @@
       </c>
       <c r="S182" t="inlineStr">
         <is>
-          <t>09-12-2021 08:30</t>
+          <t>2021-09-12 08:30:00</t>
         </is>
       </c>
       <c r="T182" t="n">
@@ -18049,7 +18049,7 @@
       </c>
       <c r="S183" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T183" t="n">
@@ -18144,7 +18144,7 @@
       </c>
       <c r="S184" t="inlineStr">
         <is>
-          <t>17-06-2021 08:30</t>
+          <t>2021-06-17 08:30:00</t>
         </is>
       </c>
       <c r="T184" t="n">
@@ -18239,7 +18239,7 @@
       </c>
       <c r="S185" t="inlineStr">
         <is>
-          <t>29-07-2021 08:30</t>
+          <t>2021-07-29 08:30:00</t>
         </is>
       </c>
       <c r="T185" t="n">
@@ -18334,7 +18334,7 @@
       </c>
       <c r="S186" t="inlineStr">
         <is>
-          <t>17-08-2021 08:30</t>
+          <t>2021-08-17 08:30:00</t>
         </is>
       </c>
       <c r="T186" t="n">
@@ -18429,7 +18429,7 @@
       </c>
       <c r="S187" t="inlineStr">
         <is>
-          <t>14-09-2021 08:30</t>
+          <t>2021-09-14 08:30:00</t>
         </is>
       </c>
       <c r="T187" t="n">
@@ -18524,7 +18524,7 @@
       </c>
       <c r="S188" t="inlineStr">
         <is>
-          <t>26-10-2021 08:30</t>
+          <t>2021-10-26 08:30:00</t>
         </is>
       </c>
       <c r="T188" t="n">
@@ -18619,7 +18619,7 @@
       </c>
       <c r="S189" t="inlineStr">
         <is>
-          <t>22-11-2021 08:30</t>
+          <t>2021-11-22 08:30:00</t>
         </is>
       </c>
       <c r="T189" t="n">
@@ -18714,7 +18714,7 @@
       </c>
       <c r="S190" t="inlineStr">
         <is>
-          <t>09-12-2021 08:30</t>
+          <t>2021-09-12 08:30:00</t>
         </is>
       </c>
       <c r="T190" t="n">
@@ -18809,7 +18809,7 @@
       </c>
       <c r="S191" t="inlineStr">
         <is>
-          <t>25-01-2021 08:30</t>
+          <t>2021-01-25 08:30:00</t>
         </is>
       </c>
       <c r="T191" t="inlineStr"/>
@@ -18902,7 +18902,7 @@
       </c>
       <c r="S192" t="inlineStr">
         <is>
-          <t>06-03-2021 08:30</t>
+          <t>2021-06-03 08:30:00</t>
         </is>
       </c>
       <c r="T192" t="inlineStr"/>
@@ -18995,7 +18995,7 @@
       </c>
       <c r="S193" t="inlineStr">
         <is>
-          <t>22-02-2021 08:30</t>
+          <t>2021-02-22 08:30:00</t>
         </is>
       </c>
       <c r="T193" t="n">
@@ -19090,7 +19090,7 @@
       </c>
       <c r="S194" t="inlineStr">
         <is>
-          <t>31-05-2021 08:30</t>
+          <t>2021-05-31 08:30:00</t>
         </is>
       </c>
       <c r="T194" t="n">
@@ -19185,7 +19185,7 @@
       </c>
       <c r="S195" t="inlineStr">
         <is>
-          <t>29-06-2021 08:30</t>
+          <t>2021-06-29 08:30:00</t>
         </is>
       </c>
       <c r="T195" t="n">
@@ -19280,7 +19280,7 @@
       </c>
       <c r="S196" t="inlineStr">
         <is>
-          <t>19-08-2021 08:30</t>
+          <t>2021-08-19 08:30:00</t>
         </is>
       </c>
       <c r="T196" t="n">
@@ -19375,7 +19375,7 @@
       </c>
       <c r="S197" t="inlineStr">
         <is>
-          <t>12-10-2021 08:30</t>
+          <t>2021-12-10 08:30:00</t>
         </is>
       </c>
       <c r="T197" t="n">
@@ -19470,7 +19470,7 @@
       </c>
       <c r="S198" t="inlineStr">
         <is>
-          <t>31-12-2021 08:30</t>
+          <t>2021-12-31 08:30:00</t>
         </is>
       </c>
       <c r="T198" t="n">
@@ -19565,7 +19565,7 @@
       </c>
       <c r="S199" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T199" t="n">
@@ -19664,7 +19664,7 @@
       </c>
       <c r="S200" t="inlineStr">
         <is>
-          <t>27-10-2021 08:30</t>
+          <t>2021-10-27 08:30:00</t>
         </is>
       </c>
       <c r="T200" t="n">
@@ -19763,7 +19763,7 @@
       </c>
       <c r="S201" t="inlineStr">
         <is>
-          <t>19-02-2021 08:30</t>
+          <t>2021-02-19 08:30:00</t>
         </is>
       </c>
       <c r="T201" t="inlineStr"/>
@@ -19856,7 +19856,7 @@
       </c>
       <c r="S202" t="inlineStr">
         <is>
-          <t>19-02-2021 08:30</t>
+          <t>2021-02-19 08:30:00</t>
         </is>
       </c>
       <c r="T202" t="inlineStr"/>
@@ -19949,7 +19949,7 @@
       </c>
       <c r="S203" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T203" t="n">
@@ -20044,7 +20044,7 @@
       </c>
       <c r="S204" t="inlineStr">
         <is>
-          <t>23-06-2021 08:30</t>
+          <t>2021-06-23 08:30:00</t>
         </is>
       </c>
       <c r="T204" t="n">
@@ -20139,7 +20139,7 @@
       </c>
       <c r="S205" t="inlineStr">
         <is>
-          <t>18-08-2021 08:30</t>
+          <t>2021-08-18 08:30:00</t>
         </is>
       </c>
       <c r="T205" t="n">
@@ -20234,7 +20234,7 @@
       </c>
       <c r="S206" t="inlineStr">
         <is>
-          <t>29-10-2021 08:30</t>
+          <t>2021-10-29 08:30:00</t>
         </is>
       </c>
       <c r="T206" t="n">
@@ -20329,7 +20329,7 @@
       </c>
       <c r="S207" t="inlineStr">
         <is>
-          <t>23-12-2021 08:30</t>
+          <t>2021-12-23 08:30:00</t>
         </is>
       </c>
       <c r="T207" t="n">
@@ -20424,7 +20424,7 @@
       </c>
       <c r="S208" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T208" t="inlineStr"/>
@@ -20517,7 +20517,7 @@
       </c>
       <c r="S209" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T209" t="inlineStr"/>
@@ -20610,7 +20610,7 @@
       </c>
       <c r="S210" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T210" t="inlineStr"/>
@@ -20703,7 +20703,7 @@
       </c>
       <c r="S211" t="inlineStr">
         <is>
-          <t>25-01-2021 08:30</t>
+          <t>2021-01-25 08:30:00</t>
         </is>
       </c>
       <c r="T211" t="inlineStr"/>
@@ -20796,7 +20796,7 @@
       </c>
       <c r="S212" t="inlineStr">
         <is>
-          <t>07-03-2021 08:30</t>
+          <t>2021-07-03 08:30:00</t>
         </is>
       </c>
       <c r="T212" t="inlineStr"/>
@@ -20889,7 +20889,7 @@
       </c>
       <c r="S213" t="inlineStr">
         <is>
-          <t>13-01-2021 08:30</t>
+          <t>2021-01-13 08:30:00</t>
         </is>
       </c>
       <c r="T213" t="n">
@@ -20984,7 +20984,7 @@
       </c>
       <c r="S214" t="inlineStr">
         <is>
-          <t>11-02-2021 08:30</t>
+          <t>2021-11-02 08:30:00</t>
         </is>
       </c>
       <c r="T214" t="n">
@@ -21079,7 +21079,7 @@
       </c>
       <c r="S215" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T215" t="n">
@@ -21174,7 +21174,7 @@
       </c>
       <c r="S216" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T216" t="n">
@@ -21269,7 +21269,7 @@
       </c>
       <c r="S217" t="inlineStr">
         <is>
-          <t>03-06-2021 08:30</t>
+          <t>2021-03-06 08:30:00</t>
         </is>
       </c>
       <c r="T217" t="n">
@@ -21364,7 +21364,7 @@
       </c>
       <c r="S218" t="inlineStr">
         <is>
-          <t>05-07-2021 08:30</t>
+          <t>2021-05-07 08:30:00</t>
         </is>
       </c>
       <c r="T218" t="n">
@@ -21459,7 +21459,7 @@
       </c>
       <c r="S219" t="inlineStr">
         <is>
-          <t>05-08-2021 08:30</t>
+          <t>2021-05-08 08:30:00</t>
         </is>
       </c>
       <c r="T219" t="n">
@@ -21554,7 +21554,7 @@
       </c>
       <c r="S220" t="inlineStr">
         <is>
-          <t>15-09-2021 08:30</t>
+          <t>2021-09-15 08:30:00</t>
         </is>
       </c>
       <c r="T220" t="n">
@@ -21649,7 +21649,7 @@
       </c>
       <c r="S221" t="inlineStr">
         <is>
-          <t>16-10-2021 08:30</t>
+          <t>2021-10-16 08:30:00</t>
         </is>
       </c>
       <c r="T221" t="n">
@@ -21744,7 +21744,7 @@
       </c>
       <c r="S222" t="inlineStr">
         <is>
-          <t>17-11-2021 08:30</t>
+          <t>2021-11-17 08:30:00</t>
         </is>
       </c>
       <c r="T222" t="n">
@@ -21839,7 +21839,7 @@
       </c>
       <c r="S223" t="inlineStr">
         <is>
-          <t>01-12-2021 08:30</t>
+          <t>2021-01-12 08:30:00</t>
         </is>
       </c>
       <c r="T223" t="n">
@@ -21934,7 +21934,7 @@
       </c>
       <c r="S224" t="inlineStr">
         <is>
-          <t>18-03-2021 08:30</t>
+          <t>2021-03-18 08:30:00</t>
         </is>
       </c>
       <c r="T224" t="inlineStr"/>
@@ -22027,7 +22027,7 @@
       </c>
       <c r="S225" t="inlineStr">
         <is>
-          <t>13-01-2021 08:30</t>
+          <t>2021-01-13 08:30:00</t>
         </is>
       </c>
       <c r="T225" t="inlineStr"/>
@@ -22120,7 +22120,7 @@
       </c>
       <c r="S226" t="inlineStr">
         <is>
-          <t>11-02-2021 08:30</t>
+          <t>2021-11-02 08:30:00</t>
         </is>
       </c>
       <c r="T226" t="inlineStr"/>
@@ -22213,7 +22213,7 @@
       </c>
       <c r="S227" t="inlineStr">
         <is>
-          <t>09-01-2021 08:30</t>
+          <t>2021-09-01 08:30:00</t>
         </is>
       </c>
       <c r="T227" t="n">
@@ -22308,7 +22308,7 @@
       </c>
       <c r="S228" t="inlineStr">
         <is>
-          <t>07-02-2021 08:30</t>
+          <t>2021-07-02 08:30:00</t>
         </is>
       </c>
       <c r="T228" t="n">
@@ -22403,7 +22403,7 @@
       </c>
       <c r="S229" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T229" t="n">
@@ -22498,7 +22498,7 @@
       </c>
       <c r="S230" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T230" t="n">
@@ -22593,7 +22593,7 @@
       </c>
       <c r="S231" t="inlineStr">
         <is>
-          <t>03-06-2021 08:30</t>
+          <t>2021-03-06 08:30:00</t>
         </is>
       </c>
       <c r="T231" t="n">
@@ -22688,7 +22688,7 @@
       </c>
       <c r="S232" t="inlineStr">
         <is>
-          <t>07-07-2021 08:30</t>
+          <t>2021-07-07 08:30:00</t>
         </is>
       </c>
       <c r="T232" t="n">
@@ -22783,7 +22783,7 @@
       </c>
       <c r="S233" t="inlineStr">
         <is>
-          <t>10-08-2021 08:30</t>
+          <t>2021-10-08 08:30:00</t>
         </is>
       </c>
       <c r="T233" t="n">
@@ -22878,7 +22878,7 @@
       </c>
       <c r="S234" t="inlineStr">
         <is>
-          <t>15-09-2021 08:30</t>
+          <t>2021-09-15 08:30:00</t>
         </is>
       </c>
       <c r="T234" t="n">
@@ -22973,7 +22973,7 @@
       </c>
       <c r="S235" t="inlineStr">
         <is>
-          <t>18-10-2021 08:30</t>
+          <t>2021-10-18 08:30:00</t>
         </is>
       </c>
       <c r="T235" t="n">
@@ -23068,7 +23068,7 @@
       </c>
       <c r="S236" t="inlineStr">
         <is>
-          <t>22-11-2021 08:30</t>
+          <t>2021-11-22 08:30:00</t>
         </is>
       </c>
       <c r="T236" t="n">
@@ -23163,7 +23163,7 @@
       </c>
       <c r="S237" t="inlineStr">
         <is>
-          <t>13-12-2021 08:30</t>
+          <t>2021-12-13 08:30:00</t>
         </is>
       </c>
       <c r="T237" t="n">
@@ -23258,7 +23258,7 @@
       </c>
       <c r="S238" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T238" t="inlineStr"/>
@@ -23351,7 +23351,7 @@
       </c>
       <c r="S239" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T239" t="inlineStr"/>
@@ -23444,7 +23444,7 @@
       </c>
       <c r="S240" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T240" t="inlineStr"/>
@@ -23537,7 +23537,7 @@
       </c>
       <c r="S241" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T241" t="n">
@@ -23636,7 +23636,7 @@
       </c>
       <c r="S242" t="inlineStr">
         <is>
-          <t>11-10-2021 08:30</t>
+          <t>2021-11-10 08:30:00</t>
         </is>
       </c>
       <c r="T242" t="n">
@@ -23735,7 +23735,7 @@
       </c>
       <c r="S243" t="inlineStr">
         <is>
-          <t>15-04-2021 08:30</t>
+          <t>2021-04-15 08:30:00</t>
         </is>
       </c>
       <c r="T243" t="n">
@@ -23834,7 +23834,7 @@
       </c>
       <c r="S244" t="inlineStr">
         <is>
-          <t>25-10-2021 08:30</t>
+          <t>2021-10-25 08:30:00</t>
         </is>
       </c>
       <c r="T244" t="n">
@@ -23933,7 +23933,7 @@
       </c>
       <c r="S245" t="inlineStr">
         <is>
-          <t>25-01-2021 08:30</t>
+          <t>2021-01-25 08:30:00</t>
         </is>
       </c>
       <c r="T245" t="n">
@@ -24028,7 +24028,7 @@
       </c>
       <c r="S246" t="inlineStr">
         <is>
-          <t>07-03-2021 08:30</t>
+          <t>2021-07-03 08:30:00</t>
         </is>
       </c>
       <c r="T246" t="n">
@@ -24123,7 +24123,7 @@
       </c>
       <c r="S247" t="inlineStr">
         <is>
-          <t>09-04-2021 08:30</t>
+          <t>2021-09-04 08:30:00</t>
         </is>
       </c>
       <c r="T247" t="n">
@@ -24218,7 +24218,7 @@
       </c>
       <c r="S248" t="inlineStr">
         <is>
-          <t>15-06-2021 08:30</t>
+          <t>2021-06-15 08:30:00</t>
         </is>
       </c>
       <c r="T248" t="n">
@@ -24313,7 +24313,7 @@
       </c>
       <c r="S249" t="inlineStr">
         <is>
-          <t>28-07-2021 08:30</t>
+          <t>2021-07-28 08:30:00</t>
         </is>
       </c>
       <c r="T249" t="n">
@@ -24408,7 +24408,7 @@
       </c>
       <c r="S250" t="inlineStr">
         <is>
-          <t>16-08-2021 08:30</t>
+          <t>2021-08-16 08:30:00</t>
         </is>
       </c>
       <c r="T250" t="n">
@@ -24503,7 +24503,7 @@
       </c>
       <c r="S251" t="inlineStr">
         <is>
-          <t>20-09-2021 08:30</t>
+          <t>2021-09-20 08:30:00</t>
         </is>
       </c>
       <c r="T251" t="n">
@@ -24598,7 +24598,7 @@
       </c>
       <c r="S252" t="inlineStr">
         <is>
-          <t>19-10-2021 08:30</t>
+          <t>2021-10-19 08:30:00</t>
         </is>
       </c>
       <c r="T252" t="n">
@@ -24693,7 +24693,7 @@
       </c>
       <c r="S253" t="inlineStr">
         <is>
-          <t>12-11-2021 08:30</t>
+          <t>2021-12-11 08:30:00</t>
         </is>
       </c>
       <c r="T253" t="n">
@@ -24788,7 +24788,7 @@
       </c>
       <c r="S254" t="inlineStr">
         <is>
-          <t>17-12-2021 08:30</t>
+          <t>2021-12-17 08:30:00</t>
         </is>
       </c>
       <c r="T254" t="n">
@@ -24883,7 +24883,7 @@
       </c>
       <c r="S255" t="inlineStr">
         <is>
-          <t>09-04-2021 08:30</t>
+          <t>2021-09-04 08:30:00</t>
         </is>
       </c>
       <c r="T255" t="n">
@@ -24978,7 +24978,7 @@
       </c>
       <c r="S256" t="inlineStr">
         <is>
-          <t>23-06-2021 08:30</t>
+          <t>2021-06-23 08:30:00</t>
         </is>
       </c>
       <c r="T256" t="n">
@@ -25073,7 +25073,7 @@
       </c>
       <c r="S257" t="inlineStr">
         <is>
-          <t>20-09-2021 08:30</t>
+          <t>2021-09-20 08:30:00</t>
         </is>
       </c>
       <c r="T257" t="n">
@@ -25168,7 +25168,7 @@
       </c>
       <c r="S258" t="inlineStr">
         <is>
-          <t>19-10-2021 08:30</t>
+          <t>2021-10-19 08:30:00</t>
         </is>
       </c>
       <c r="T258" t="n">
@@ -25263,7 +25263,7 @@
       </c>
       <c r="S259" t="inlineStr">
         <is>
-          <t>17-12-2021 08:30</t>
+          <t>2021-12-17 08:30:00</t>
         </is>
       </c>
       <c r="T259" t="n">
@@ -25358,7 +25358,7 @@
       </c>
       <c r="S260" t="inlineStr">
         <is>
-          <t>15-04-2021 08:30</t>
+          <t>2021-04-15 08:30:00</t>
         </is>
       </c>
       <c r="T260" t="n">
@@ -25457,7 +25457,7 @@
       </c>
       <c r="S261" t="inlineStr">
         <is>
-          <t>11-10-2021 08:30</t>
+          <t>2021-11-10 08:30:00</t>
         </is>
       </c>
       <c r="T261" t="n">
@@ -25556,7 +25556,7 @@
       </c>
       <c r="S262" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T262" t="n">
@@ -25655,7 +25655,7 @@
       </c>
       <c r="S263" t="inlineStr">
         <is>
-          <t>27-10-2021 08:30</t>
+          <t>2021-10-27 08:30:00</t>
         </is>
       </c>
       <c r="T263" t="n">
@@ -25754,7 +25754,7 @@
       </c>
       <c r="S264" t="inlineStr">
         <is>
-          <t>12-04-2021 08:30</t>
+          <t>2021-12-04 08:30:00</t>
         </is>
       </c>
       <c r="T264" t="n">
@@ -25853,7 +25853,7 @@
       </c>
       <c r="S265" t="inlineStr">
         <is>
-          <t>14-10-2021 08:30</t>
+          <t>2021-10-14 08:30:00</t>
         </is>
       </c>
       <c r="T265" t="n">
@@ -25952,7 +25952,7 @@
       </c>
       <c r="S266" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T266" t="n">
@@ -26051,7 +26051,7 @@
       </c>
       <c r="S267" t="inlineStr">
         <is>
-          <t>26-10-2021 08:30</t>
+          <t>2021-10-26 08:30:00</t>
         </is>
       </c>
       <c r="T267" t="n">
@@ -26150,7 +26150,7 @@
       </c>
       <c r="S268" t="inlineStr">
         <is>
-          <t>15-04-2021 08:30</t>
+          <t>2021-04-15 08:30:00</t>
         </is>
       </c>
       <c r="T268" t="n">
@@ -26249,7 +26249,7 @@
       </c>
       <c r="S269" t="inlineStr">
         <is>
-          <t>11-10-2021 08:30</t>
+          <t>2021-11-10 08:30:00</t>
         </is>
       </c>
       <c r="T269" t="n">
@@ -26348,7 +26348,7 @@
       </c>
       <c r="S270" t="inlineStr">
         <is>
-          <t>15-04-2021 08:30</t>
+          <t>2021-04-15 08:30:00</t>
         </is>
       </c>
       <c r="T270" t="n">
@@ -26447,7 +26447,7 @@
       </c>
       <c r="S271" t="inlineStr">
         <is>
-          <t>11-10-2021 08:30</t>
+          <t>2021-11-10 08:30:00</t>
         </is>
       </c>
       <c r="T271" t="n">
@@ -26546,7 +26546,7 @@
       </c>
       <c r="S272" t="inlineStr">
         <is>
-          <t>12-04-2021 08:30</t>
+          <t>2021-12-04 08:30:00</t>
         </is>
       </c>
       <c r="T272" t="n">
@@ -26645,7 +26645,7 @@
       </c>
       <c r="S273" t="inlineStr">
         <is>
-          <t>14-10-2021 08:30</t>
+          <t>2021-10-14 08:30:00</t>
         </is>
       </c>
       <c r="T273" t="n">
@@ -26744,7 +26744,7 @@
       </c>
       <c r="S274" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T274" t="n">
@@ -26843,7 +26843,7 @@
       </c>
       <c r="S275" t="inlineStr">
         <is>
-          <t>27-10-2021 08:30</t>
+          <t>2021-10-27 08:30:00</t>
         </is>
       </c>
       <c r="T275" t="n">
@@ -26942,7 +26942,7 @@
       </c>
       <c r="S276" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T276" t="n">
@@ -27041,7 +27041,7 @@
       </c>
       <c r="S277" t="inlineStr">
         <is>
-          <t>26-10-2021 08:30</t>
+          <t>2021-10-26 08:30:00</t>
         </is>
       </c>
       <c r="T277" t="n">
@@ -27140,7 +27140,7 @@
       </c>
       <c r="S278" t="inlineStr">
         <is>
-          <t>12-04-2021 08:30</t>
+          <t>2021-12-04 08:30:00</t>
         </is>
       </c>
       <c r="T278" t="n">
@@ -27239,7 +27239,7 @@
       </c>
       <c r="S279" t="inlineStr">
         <is>
-          <t>14-10-2021 08:30</t>
+          <t>2021-10-14 08:30:00</t>
         </is>
       </c>
       <c r="T279" t="n">
@@ -27338,7 +27338,7 @@
       </c>
       <c r="S280" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T280" t="n">
@@ -27433,7 +27433,7 @@
       </c>
       <c r="S281" t="inlineStr">
         <is>
-          <t>12-02-2021 08:30</t>
+          <t>2021-12-02 08:30:00</t>
         </is>
       </c>
       <c r="T281" t="n">
@@ -27528,7 +27528,7 @@
       </c>
       <c r="S282" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T282" t="n">
@@ -27623,7 +27623,7 @@
       </c>
       <c r="S283" t="inlineStr">
         <is>
-          <t>12-04-2021 08:30</t>
+          <t>2021-12-04 08:30:00</t>
         </is>
       </c>
       <c r="T283" t="n">
@@ -27718,7 +27718,7 @@
       </c>
       <c r="S284" t="inlineStr">
         <is>
-          <t>25-05-2021 08:30</t>
+          <t>2021-05-25 08:30:00</t>
         </is>
       </c>
       <c r="T284" t="n">
@@ -27813,7 +27813,7 @@
       </c>
       <c r="S285" t="inlineStr">
         <is>
-          <t>16-06-2021 08:30</t>
+          <t>2021-06-16 08:30:00</t>
         </is>
       </c>
       <c r="T285" t="n">
@@ -27908,7 +27908,7 @@
       </c>
       <c r="S286" t="inlineStr">
         <is>
-          <t>19-07-2021 08:30</t>
+          <t>2021-07-19 08:30:00</t>
         </is>
       </c>
       <c r="T286" t="n">
@@ -28003,7 +28003,7 @@
       </c>
       <c r="S287" t="inlineStr">
         <is>
-          <t>16-08-2021 08:30</t>
+          <t>2021-08-16 08:30:00</t>
         </is>
       </c>
       <c r="T287" t="n">
@@ -28098,7 +28098,7 @@
       </c>
       <c r="S288" t="inlineStr">
         <is>
-          <t>08-09-2021 08:30</t>
+          <t>2021-08-09 08:30:00</t>
         </is>
       </c>
       <c r="T288" t="n">
@@ -28193,7 +28193,7 @@
       </c>
       <c r="S289" t="inlineStr">
         <is>
-          <t>14-10-2021 08:30</t>
+          <t>2021-10-14 08:30:00</t>
         </is>
       </c>
       <c r="T289" t="n">
@@ -28288,7 +28288,7 @@
       </c>
       <c r="S290" t="inlineStr">
         <is>
-          <t>11-11-2021 08:30</t>
+          <t>2021-11-11 08:30:00</t>
         </is>
       </c>
       <c r="T290" t="n">
@@ -28383,7 +28383,7 @@
       </c>
       <c r="S291" t="inlineStr">
         <is>
-          <t>09-12-2021 08:30</t>
+          <t>2021-09-12 08:30:00</t>
         </is>
       </c>
       <c r="T291" t="n">
@@ -28478,7 +28478,7 @@
       </c>
       <c r="S292" t="inlineStr">
         <is>
-          <t>12-04-2021 08:30</t>
+          <t>2021-12-04 08:30:00</t>
         </is>
       </c>
       <c r="T292" t="n">
@@ -28577,7 +28577,7 @@
       </c>
       <c r="S293" t="inlineStr">
         <is>
-          <t>14-10-2021 08:30</t>
+          <t>2021-10-14 08:30:00</t>
         </is>
       </c>
       <c r="T293" t="n">
@@ -28676,7 +28676,7 @@
       </c>
       <c r="S294" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T294" t="n">
@@ -28775,7 +28775,7 @@
       </c>
       <c r="S295" t="inlineStr">
         <is>
-          <t>27-10-2021 08:30</t>
+          <t>2021-10-27 08:30:00</t>
         </is>
       </c>
       <c r="T295" t="n">
@@ -28874,7 +28874,7 @@
       </c>
       <c r="S296" t="inlineStr">
         <is>
-          <t>12-04-2021 08:30</t>
+          <t>2021-12-04 08:30:00</t>
         </is>
       </c>
       <c r="T296" t="n">
@@ -28973,7 +28973,7 @@
       </c>
       <c r="S297" t="inlineStr">
         <is>
-          <t>14-10-2021 08:30</t>
+          <t>2021-10-14 08:30:00</t>
         </is>
       </c>
       <c r="T297" t="n">
@@ -29072,7 +29072,7 @@
       </c>
       <c r="S298" t="inlineStr">
         <is>
-          <t>09-04-2021 08:30</t>
+          <t>2021-09-04 08:30:00</t>
         </is>
       </c>
       <c r="T298" t="n">
@@ -29171,7 +29171,7 @@
       </c>
       <c r="S299" t="inlineStr">
         <is>
-          <t>11-10-2021 08:30</t>
+          <t>2021-11-10 08:30:00</t>
         </is>
       </c>
       <c r="T299" t="n">
@@ -29270,7 +29270,7 @@
       </c>
       <c r="S300" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T300" t="n">
@@ -29369,7 +29369,7 @@
       </c>
       <c r="S301" t="inlineStr">
         <is>
-          <t>29-10-2021 08:30</t>
+          <t>2021-10-29 08:30:00</t>
         </is>
       </c>
       <c r="T301" t="n">
@@ -29468,7 +29468,7 @@
       </c>
       <c r="S302" t="inlineStr">
         <is>
-          <t>19-02-2021 08:30</t>
+          <t>2021-02-19 08:30:00</t>
         </is>
       </c>
       <c r="T302" t="inlineStr"/>
@@ -29561,7 +29561,7 @@
       </c>
       <c r="S303" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T303" t="n">
@@ -29660,7 +29660,7 @@
       </c>
       <c r="S304" t="inlineStr">
         <is>
-          <t>26-10-2021 08:30</t>
+          <t>2021-10-26 08:30:00</t>
         </is>
       </c>
       <c r="T304" t="n">
@@ -29759,7 +29759,7 @@
       </c>
       <c r="S305" t="inlineStr">
         <is>
-          <t>12-02-2021 08:30</t>
+          <t>2021-12-02 08:30:00</t>
         </is>
       </c>
       <c r="T305" t="n">
@@ -29854,7 +29854,7 @@
       </c>
       <c r="S306" t="inlineStr">
         <is>
-          <t>12-04-2021 08:30</t>
+          <t>2021-12-04 08:30:00</t>
         </is>
       </c>
       <c r="T306" t="n">
@@ -29949,7 +29949,7 @@
       </c>
       <c r="S307" t="inlineStr">
         <is>
-          <t>16-06-2021 08:30</t>
+          <t>2021-06-16 08:30:00</t>
         </is>
       </c>
       <c r="T307" t="n">
@@ -30044,7 +30044,7 @@
       </c>
       <c r="S308" t="inlineStr">
         <is>
-          <t>16-08-2021 08:30</t>
+          <t>2021-08-16 08:30:00</t>
         </is>
       </c>
       <c r="T308" t="n">
@@ -30139,7 +30139,7 @@
       </c>
       <c r="S309" t="inlineStr">
         <is>
-          <t>14-10-2021 08:30</t>
+          <t>2021-10-14 08:30:00</t>
         </is>
       </c>
       <c r="T309" t="n">
@@ -30234,7 +30234,7 @@
       </c>
       <c r="S310" t="inlineStr">
         <is>
-          <t>09-12-2021 08:30</t>
+          <t>2021-09-12 08:30:00</t>
         </is>
       </c>
       <c r="T310" t="n">
@@ -30329,7 +30329,7 @@
       </c>
       <c r="S311" t="inlineStr">
         <is>
-          <t>16-02-2021 08:30</t>
+          <t>2021-02-16 08:30:00</t>
         </is>
       </c>
       <c r="T311" t="inlineStr"/>
@@ -30422,7 +30422,7 @@
       </c>
       <c r="S312" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T312" t="n">
@@ -30521,7 +30521,7 @@
       </c>
       <c r="S313" t="inlineStr">
         <is>
-          <t>27-10-2021 08:30</t>
+          <t>2021-10-27 08:30:00</t>
         </is>
       </c>
       <c r="T313" t="n">
@@ -30620,7 +30620,7 @@
       </c>
       <c r="S314" t="inlineStr">
         <is>
-          <t>07-04-2021 08:30</t>
+          <t>2021-07-04 08:30:00</t>
         </is>
       </c>
       <c r="T314" t="n">
@@ -30719,7 +30719,7 @@
       </c>
       <c r="S315" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T315" t="n">
@@ -30818,7 +30818,7 @@
       </c>
       <c r="S316" t="inlineStr">
         <is>
-          <t>14-01-2021 08:30</t>
+          <t>2021-01-14 08:30:00</t>
         </is>
       </c>
       <c r="T316" t="n">
@@ -30913,7 +30913,7 @@
       </c>
       <c r="S317" t="inlineStr">
         <is>
-          <t>12-02-2021 08:30</t>
+          <t>2021-12-02 08:30:00</t>
         </is>
       </c>
       <c r="T317" t="n">
@@ -31008,7 +31008,7 @@
       </c>
       <c r="S318" t="inlineStr">
         <is>
-          <t>18-03-2021 08:30</t>
+          <t>2021-03-18 08:30:00</t>
         </is>
       </c>
       <c r="T318" t="n">
@@ -31103,7 +31103,7 @@
       </c>
       <c r="S319" t="inlineStr">
         <is>
-          <t>15-04-2021 08:30</t>
+          <t>2021-04-15 08:30:00</t>
         </is>
       </c>
       <c r="T319" t="n">
@@ -31198,7 +31198,7 @@
       </c>
       <c r="S320" t="inlineStr">
         <is>
-          <t>30-05-2021 08:30</t>
+          <t>2021-05-30 08:30:00</t>
         </is>
       </c>
       <c r="T320" t="n">
@@ -31293,7 +31293,7 @@
       </c>
       <c r="S321" t="inlineStr">
         <is>
-          <t>24-06-2021 08:30</t>
+          <t>2021-06-24 08:30:00</t>
         </is>
       </c>
       <c r="T321" t="n">
@@ -31388,7 +31388,7 @@
       </c>
       <c r="S322" t="inlineStr">
         <is>
-          <t>19-07-2021 08:30</t>
+          <t>2021-07-19 08:30:00</t>
         </is>
       </c>
       <c r="T322" t="n">
@@ -31483,7 +31483,7 @@
       </c>
       <c r="S323" t="inlineStr">
         <is>
-          <t>24-08-2021 08:30</t>
+          <t>2021-08-24 08:30:00</t>
         </is>
       </c>
       <c r="T323" t="n">
@@ -31578,7 +31578,7 @@
       </c>
       <c r="S324" t="inlineStr">
         <is>
-          <t>28-09-2021 08:30</t>
+          <t>2021-09-28 08:30:00</t>
         </is>
       </c>
       <c r="T324" t="n">
@@ -31673,7 +31673,7 @@
       </c>
       <c r="S325" t="inlineStr">
         <is>
-          <t>11-10-2021 08:30</t>
+          <t>2021-11-10 08:30:00</t>
         </is>
       </c>
       <c r="T325" t="n">
@@ -31768,7 +31768,7 @@
       </c>
       <c r="S326" t="inlineStr">
         <is>
-          <t>09-11-2021 08:30</t>
+          <t>2021-09-11 08:30:00</t>
         </is>
       </c>
       <c r="T326" t="n">
@@ -31863,7 +31863,7 @@
       </c>
       <c r="S327" t="inlineStr">
         <is>
-          <t>16-12-2021 08:30</t>
+          <t>2021-12-16 08:30:00</t>
         </is>
       </c>
       <c r="T327" t="n">
@@ -31958,7 +31958,7 @@
       </c>
       <c r="S328" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T328" t="n">
@@ -32053,7 +32053,7 @@
       </c>
       <c r="S329" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T329" t="n">
@@ -32148,7 +32148,7 @@
       </c>
       <c r="S330" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T330" t="n">
@@ -32243,7 +32243,7 @@
       </c>
       <c r="S331" t="inlineStr">
         <is>
-          <t>04-04-2021 08:30</t>
+          <t>2021-04-04 08:30:00</t>
         </is>
       </c>
       <c r="T331" t="n">
@@ -32338,7 +32338,7 @@
       </c>
       <c r="S332" t="inlineStr">
         <is>
-          <t>22-06-2021 08:30</t>
+          <t>2021-06-22 08:30:00</t>
         </is>
       </c>
       <c r="T332" t="n">
@@ -32433,7 +32433,7 @@
       </c>
       <c r="S333" t="inlineStr">
         <is>
-          <t>19-07-2021 08:30</t>
+          <t>2021-07-19 08:30:00</t>
         </is>
       </c>
       <c r="T333" t="n">
@@ -32528,7 +32528,7 @@
       </c>
       <c r="S334" t="inlineStr">
         <is>
-          <t>10-08-2021 08:30</t>
+          <t>2021-10-08 08:30:00</t>
         </is>
       </c>
       <c r="T334" t="n">
@@ -32623,7 +32623,7 @@
       </c>
       <c r="S335" t="inlineStr">
         <is>
-          <t>08-09-2021 08:30</t>
+          <t>2021-08-09 08:30:00</t>
         </is>
       </c>
       <c r="T335" t="n">
@@ -32718,7 +32718,7 @@
       </c>
       <c r="S336" t="inlineStr">
         <is>
-          <t>11-10-2021 08:30</t>
+          <t>2021-11-10 08:30:00</t>
         </is>
       </c>
       <c r="T336" t="n">
@@ -32813,7 +32813,7 @@
       </c>
       <c r="S337" t="inlineStr">
         <is>
-          <t>10-11-2021 08:30</t>
+          <t>2021-10-11 08:30:00</t>
         </is>
       </c>
       <c r="T337" t="n">
@@ -32908,7 +32908,7 @@
       </c>
       <c r="S338" t="inlineStr">
         <is>
-          <t>09-12-2021 08:30</t>
+          <t>2021-09-12 08:30:00</t>
         </is>
       </c>
       <c r="T338" t="n">
@@ -33003,7 +33003,7 @@
       </c>
       <c r="S339" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T339" t="n">
@@ -33098,7 +33098,7 @@
       </c>
       <c r="S340" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T340" t="n">
@@ -33193,7 +33193,7 @@
       </c>
       <c r="S341" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T341" t="n">
@@ -33288,7 +33288,7 @@
       </c>
       <c r="S342" t="inlineStr">
         <is>
-          <t>04-04-2021 08:30</t>
+          <t>2021-04-04 08:30:00</t>
         </is>
       </c>
       <c r="T342" t="n">
@@ -33383,7 +33383,7 @@
       </c>
       <c r="S343" t="inlineStr">
         <is>
-          <t>22-06-2021 08:30</t>
+          <t>2021-06-22 08:30:00</t>
         </is>
       </c>
       <c r="T343" t="n">
@@ -33478,7 +33478,7 @@
       </c>
       <c r="S344" t="inlineStr">
         <is>
-          <t>19-07-2021 08:30</t>
+          <t>2021-07-19 08:30:00</t>
         </is>
       </c>
       <c r="T344" t="n">
@@ -33573,7 +33573,7 @@
       </c>
       <c r="S345" t="inlineStr">
         <is>
-          <t>10-08-2021 08:30</t>
+          <t>2021-10-08 08:30:00</t>
         </is>
       </c>
       <c r="T345" t="n">
@@ -33668,7 +33668,7 @@
       </c>
       <c r="S346" t="inlineStr">
         <is>
-          <t>08-09-2021 08:30</t>
+          <t>2021-08-09 08:30:00</t>
         </is>
       </c>
       <c r="T346" t="n">
@@ -33763,7 +33763,7 @@
       </c>
       <c r="S347" t="inlineStr">
         <is>
-          <t>11-10-2021 08:30</t>
+          <t>2021-11-10 08:30:00</t>
         </is>
       </c>
       <c r="T347" t="n">
@@ -33858,7 +33858,7 @@
       </c>
       <c r="S348" t="inlineStr">
         <is>
-          <t>10-11-2021 08:30</t>
+          <t>2021-10-11 08:30:00</t>
         </is>
       </c>
       <c r="T348" t="n">
@@ -33953,7 +33953,7 @@
       </c>
       <c r="S349" t="inlineStr">
         <is>
-          <t>09-12-2021 08:30</t>
+          <t>2021-09-12 08:30:00</t>
         </is>
       </c>
       <c r="T349" t="n">
@@ -34048,7 +34048,7 @@
       </c>
       <c r="S350" t="inlineStr">
         <is>
-          <t>25-01-2021 08:30</t>
+          <t>2021-01-25 08:30:00</t>
         </is>
       </c>
       <c r="T350" t="inlineStr"/>
@@ -34141,7 +34141,7 @@
       </c>
       <c r="S351" t="inlineStr">
         <is>
-          <t>06-03-2021 08:30</t>
+          <t>2021-06-03 08:30:00</t>
         </is>
       </c>
       <c r="T351" t="inlineStr"/>
@@ -34234,7 +34234,7 @@
       </c>
       <c r="S352" t="inlineStr">
         <is>
-          <t>15-04-2021 08:30</t>
+          <t>2021-04-15 08:30:00</t>
         </is>
       </c>
       <c r="T352" t="n">
@@ -34333,7 +34333,7 @@
       </c>
       <c r="S353" t="inlineStr">
         <is>
-          <t>25-10-2021 08:30</t>
+          <t>2021-10-25 08:30:00</t>
         </is>
       </c>
       <c r="T353" t="n">
@@ -34432,7 +34432,7 @@
       </c>
       <c r="S354" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T354" t="n">
@@ -34531,7 +34531,7 @@
       </c>
       <c r="S355" t="inlineStr">
         <is>
-          <t>29-10-2021 08:30</t>
+          <t>2021-10-29 08:30:00</t>
         </is>
       </c>
       <c r="T355" t="n">
@@ -34630,7 +34630,7 @@
       </c>
       <c r="S356" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T356" t="n">
@@ -34729,7 +34729,7 @@
       </c>
       <c r="S357" t="inlineStr">
         <is>
-          <t>29-10-2021 08:30</t>
+          <t>2021-10-29 08:30:00</t>
         </is>
       </c>
       <c r="T357" t="n">
@@ -34828,7 +34828,7 @@
       </c>
       <c r="S358" t="inlineStr">
         <is>
-          <t>14-04-2021 08:30</t>
+          <t>2021-04-14 08:30:00</t>
         </is>
       </c>
       <c r="T358" t="n">
@@ -34927,7 +34927,7 @@
       </c>
       <c r="S359" t="inlineStr">
         <is>
-          <t>24-10-2021 08:30</t>
+          <t>2021-10-24 08:30:00</t>
         </is>
       </c>
       <c r="T359" t="inlineStr"/>
@@ -35024,7 +35024,7 @@
       </c>
       <c r="S360" t="inlineStr">
         <is>
-          <t>14-04-2021 08:30</t>
+          <t>2021-04-14 08:30:00</t>
         </is>
       </c>
       <c r="T360" t="n">
@@ -35123,7 +35123,7 @@
       </c>
       <c r="S361" t="inlineStr">
         <is>
-          <t>24-10-2021 08:30</t>
+          <t>2021-10-24 08:30:00</t>
         </is>
       </c>
       <c r="T361" t="n">
@@ -35222,7 +35222,7 @@
       </c>
       <c r="S362" t="inlineStr">
         <is>
-          <t>14-04-2021 08:30</t>
+          <t>2021-04-14 08:30:00</t>
         </is>
       </c>
       <c r="T362" t="n">
@@ -35321,7 +35321,7 @@
       </c>
       <c r="S363" t="inlineStr">
         <is>
-          <t>24-10-2021 08:30</t>
+          <t>2021-10-24 08:30:00</t>
         </is>
       </c>
       <c r="T363" t="n">
@@ -35420,7 +35420,7 @@
       </c>
       <c r="S364" t="inlineStr">
         <is>
-          <t>14-04-2021 08:30</t>
+          <t>2021-04-14 08:30:00</t>
         </is>
       </c>
       <c r="T364" t="n">
@@ -35519,7 +35519,7 @@
       </c>
       <c r="S365" t="inlineStr">
         <is>
-          <t>24-10-2021 08:30</t>
+          <t>2021-10-24 08:30:00</t>
         </is>
       </c>
       <c r="T365" t="n">
@@ -35618,7 +35618,7 @@
       </c>
       <c r="S366" t="inlineStr">
         <is>
-          <t>29-10-2021 08:30</t>
+          <t>2021-10-29 08:30:00</t>
         </is>
       </c>
       <c r="T366" t="n">
@@ -35717,7 +35717,7 @@
       </c>
       <c r="S367" t="inlineStr">
         <is>
-          <t>15-01-2021 08:30</t>
+          <t>2021-01-15 08:30:00</t>
         </is>
       </c>
       <c r="T367" t="inlineStr"/>
@@ -35810,7 +35810,7 @@
       </c>
       <c r="S368" t="inlineStr">
         <is>
-          <t>11-02-2021 08:30</t>
+          <t>2021-11-02 08:30:00</t>
         </is>
       </c>
       <c r="T368" t="inlineStr"/>
@@ -35903,7 +35903,7 @@
       </c>
       <c r="S369" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T369" t="inlineStr"/>
@@ -35996,7 +35996,7 @@
       </c>
       <c r="S370" t="inlineStr">
         <is>
-          <t>22-01-2021 08:30</t>
+          <t>2021-01-22 08:30:00</t>
         </is>
       </c>
       <c r="T370" t="inlineStr"/>
@@ -36089,7 +36089,7 @@
       </c>
       <c r="S371" t="inlineStr">
         <is>
-          <t>22-02-2021 08:30</t>
+          <t>2021-02-22 08:30:00</t>
         </is>
       </c>
       <c r="T371" t="inlineStr"/>
@@ -36182,7 +36182,7 @@
       </c>
       <c r="S372" t="inlineStr">
         <is>
-          <t>19-03-2021 08:30</t>
+          <t>2021-03-19 08:30:00</t>
         </is>
       </c>
       <c r="T372" t="inlineStr"/>
@@ -36275,7 +36275,7 @@
       </c>
       <c r="S373" t="inlineStr">
         <is>
-          <t>01-01-2021 08:30</t>
+          <t>2021-01-01 08:30:00</t>
         </is>
       </c>
       <c r="T373" t="inlineStr"/>
@@ -36368,7 +36368,7 @@
       </c>
       <c r="S374" t="inlineStr">
         <is>
-          <t>22-02-2021 08:30</t>
+          <t>2021-02-22 08:30:00</t>
         </is>
       </c>
       <c r="T374" t="inlineStr"/>
@@ -36461,7 +36461,7 @@
       </c>
       <c r="S375" t="inlineStr">
         <is>
-          <t>19-03-2021 08:30</t>
+          <t>2021-03-19 08:30:00</t>
         </is>
       </c>
       <c r="T375" t="inlineStr"/>
@@ -36554,7 +36554,7 @@
       </c>
       <c r="S376" t="inlineStr">
         <is>
-          <t>14-01-2021 08:30</t>
+          <t>2021-01-14 08:30:00</t>
         </is>
       </c>
       <c r="T376" t="inlineStr"/>
@@ -36647,7 +36647,7 @@
       </c>
       <c r="S377" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T377" t="inlineStr"/>
@@ -36740,7 +36740,7 @@
       </c>
       <c r="S378" t="inlineStr">
         <is>
-          <t>07-04-2021 08:30</t>
+          <t>2021-07-04 08:30:00</t>
         </is>
       </c>
       <c r="T378" t="n">
@@ -36839,7 +36839,7 @@
       </c>
       <c r="S379" t="inlineStr">
         <is>
-          <t>18-10-2021 08:30</t>
+          <t>2021-10-18 08:30:00</t>
         </is>
       </c>
       <c r="T379" t="n">
@@ -36938,7 +36938,7 @@
       </c>
       <c r="S380" t="inlineStr">
         <is>
-          <t>12-06-2021 08:30</t>
+          <t>2021-12-06 08:30:00</t>
         </is>
       </c>
       <c r="T380" t="n">
@@ -37037,7 +37037,7 @@
       </c>
       <c r="S381" t="inlineStr">
         <is>
-          <t>18-10-2021 08:30</t>
+          <t>2021-10-18 08:30:00</t>
         </is>
       </c>
       <c r="T381" t="n">
@@ -37136,7 +37136,7 @@
       </c>
       <c r="S382" t="inlineStr">
         <is>
-          <t>12-06-2021 08:30</t>
+          <t>2021-12-06 08:30:00</t>
         </is>
       </c>
       <c r="T382" t="n">
@@ -37235,7 +37235,7 @@
       </c>
       <c r="S383" t="inlineStr">
         <is>
-          <t>18-10-2021 08:30</t>
+          <t>2021-10-18 08:30:00</t>
         </is>
       </c>
       <c r="T383" t="n">
@@ -37334,7 +37334,7 @@
       </c>
       <c r="S384" t="inlineStr">
         <is>
-          <t>12-06-2021 08:30</t>
+          <t>2021-12-06 08:30:00</t>
         </is>
       </c>
       <c r="T384" t="n">
@@ -37433,7 +37433,7 @@
       </c>
       <c r="S385" t="inlineStr">
         <is>
-          <t>18-10-2021 08:30</t>
+          <t>2021-10-18 08:30:00</t>
         </is>
       </c>
       <c r="T385" t="n">
@@ -37532,7 +37532,7 @@
       </c>
       <c r="S386" t="inlineStr">
         <is>
-          <t>12-06-2021 08:30</t>
+          <t>2021-12-06 08:30:00</t>
         </is>
       </c>
       <c r="T386" t="n">
@@ -37631,7 +37631,7 @@
       </c>
       <c r="S387" t="inlineStr">
         <is>
-          <t>18-10-2021 08:30</t>
+          <t>2021-10-18 08:30:00</t>
         </is>
       </c>
       <c r="T387" t="n">
@@ -37730,7 +37730,7 @@
       </c>
       <c r="S388" t="inlineStr">
         <is>
-          <t>12-06-2021 08:30</t>
+          <t>2021-12-06 08:30:00</t>
         </is>
       </c>
       <c r="T388" t="n">
@@ -37829,7 +37829,7 @@
       </c>
       <c r="S389" t="inlineStr">
         <is>
-          <t>18-10-2021 08:30</t>
+          <t>2021-10-18 08:30:00</t>
         </is>
       </c>
       <c r="T389" t="n">
@@ -37928,7 +37928,7 @@
       </c>
       <c r="S390" t="inlineStr">
         <is>
-          <t>12-06-2021 08:30</t>
+          <t>2021-12-06 08:30:00</t>
         </is>
       </c>
       <c r="T390" t="n">
@@ -38027,7 +38027,7 @@
       </c>
       <c r="S391" t="inlineStr">
         <is>
-          <t>18-10-2021 08:30</t>
+          <t>2021-10-18 08:30:00</t>
         </is>
       </c>
       <c r="T391" t="n">
@@ -38126,7 +38126,7 @@
       </c>
       <c r="S392" t="inlineStr">
         <is>
-          <t>12-06-2021 08:30</t>
+          <t>2021-12-06 08:30:00</t>
         </is>
       </c>
       <c r="T392" t="n">
@@ -38225,7 +38225,7 @@
       </c>
       <c r="S393" t="inlineStr">
         <is>
-          <t>18-10-2021 08:30</t>
+          <t>2021-10-18 08:30:00</t>
         </is>
       </c>
       <c r="T393" t="n">
@@ -38324,7 +38324,7 @@
       </c>
       <c r="S394" t="inlineStr">
         <is>
-          <t>15-04-2021 08:30</t>
+          <t>2021-04-15 08:30:00</t>
         </is>
       </c>
       <c r="T394" t="n">
@@ -38419,7 +38419,7 @@
       </c>
       <c r="S395" t="inlineStr">
         <is>
-          <t>17-06-2021 08:30</t>
+          <t>2021-06-17 08:30:00</t>
         </is>
       </c>
       <c r="T395" t="n">
@@ -38514,7 +38514,7 @@
       </c>
       <c r="S396" t="inlineStr">
         <is>
-          <t>17-08-2021 08:30</t>
+          <t>2021-08-17 08:30:00</t>
         </is>
       </c>
       <c r="T396" t="n">
@@ -38609,7 +38609,7 @@
       </c>
       <c r="S397" t="inlineStr">
         <is>
-          <t>24-10-2021 08:30</t>
+          <t>2021-10-24 08:30:00</t>
         </is>
       </c>
       <c r="T397" t="n">
@@ -38704,7 +38704,7 @@
       </c>
       <c r="S398" t="inlineStr">
         <is>
-          <t>30-12-2021 08:30</t>
+          <t>2021-12-30 08:30:00</t>
         </is>
       </c>
       <c r="T398" t="n">
@@ -38799,7 +38799,7 @@
       </c>
       <c r="S399" t="inlineStr">
         <is>
-          <t>15-04-2021 08:30</t>
+          <t>2021-04-15 08:30:00</t>
         </is>
       </c>
       <c r="T399" t="n">
@@ -38898,7 +38898,7 @@
       </c>
       <c r="S400" t="inlineStr">
         <is>
-          <t>14-10-2021 08:30</t>
+          <t>2021-10-14 08:30:00</t>
         </is>
       </c>
       <c r="T400" t="n">
@@ -38997,7 +38997,7 @@
       </c>
       <c r="S401" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T401" t="n">
@@ -39092,7 +39092,7 @@
       </c>
       <c r="S402" t="inlineStr">
         <is>
-          <t>12-02-2021 08:30</t>
+          <t>2021-12-02 08:30:00</t>
         </is>
       </c>
       <c r="T402" t="n">
@@ -39187,7 +39187,7 @@
       </c>
       <c r="S403" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T403" t="n">
@@ -39282,7 +39282,7 @@
       </c>
       <c r="S404" t="inlineStr">
         <is>
-          <t>12-04-2021 08:30</t>
+          <t>2021-12-04 08:30:00</t>
         </is>
       </c>
       <c r="T404" t="n">
@@ -39377,7 +39377,7 @@
       </c>
       <c r="S405" t="inlineStr">
         <is>
-          <t>25-05-2021 08:30</t>
+          <t>2021-05-25 08:30:00</t>
         </is>
       </c>
       <c r="T405" t="n">
@@ -39472,7 +39472,7 @@
       </c>
       <c r="S406" t="inlineStr">
         <is>
-          <t>16-06-2021 08:30</t>
+          <t>2021-06-16 08:30:00</t>
         </is>
       </c>
       <c r="T406" t="n">
@@ -39567,7 +39567,7 @@
       </c>
       <c r="S407" t="inlineStr">
         <is>
-          <t>19-07-2021 08:30</t>
+          <t>2021-07-19 08:30:00</t>
         </is>
       </c>
       <c r="T407" t="n">
@@ -39662,7 +39662,7 @@
       </c>
       <c r="S408" t="inlineStr">
         <is>
-          <t>16-08-2021 08:30</t>
+          <t>2021-08-16 08:30:00</t>
         </is>
       </c>
       <c r="T408" t="n">
@@ -39757,7 +39757,7 @@
       </c>
       <c r="S409" t="inlineStr">
         <is>
-          <t>08-09-2021 08:30</t>
+          <t>2021-08-09 08:30:00</t>
         </is>
       </c>
       <c r="T409" t="n">
@@ -39852,7 +39852,7 @@
       </c>
       <c r="S410" t="inlineStr">
         <is>
-          <t>14-10-2021 08:30</t>
+          <t>2021-10-14 08:30:00</t>
         </is>
       </c>
       <c r="T410" t="n">
@@ -39947,7 +39947,7 @@
       </c>
       <c r="S411" t="inlineStr">
         <is>
-          <t>11-11-2021 08:30</t>
+          <t>2021-11-11 08:30:00</t>
         </is>
       </c>
       <c r="T411" t="n">
@@ -40042,7 +40042,7 @@
       </c>
       <c r="S412" t="inlineStr">
         <is>
-          <t>09-12-2021 08:30</t>
+          <t>2021-09-12 08:30:00</t>
         </is>
       </c>
       <c r="T412" t="n">
@@ -40137,7 +40137,7 @@
       </c>
       <c r="S413" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T413" t="n">
@@ -40236,7 +40236,7 @@
       </c>
       <c r="S414" t="inlineStr">
         <is>
-          <t>07-04-2021 08:30</t>
+          <t>2021-07-04 08:30:00</t>
         </is>
       </c>
       <c r="T414" t="n">
@@ -40335,7 +40335,7 @@
       </c>
       <c r="S415" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T415" t="n">
@@ -40434,7 +40434,7 @@
       </c>
       <c r="S416" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T416" t="n">
@@ -40533,7 +40533,7 @@
       </c>
       <c r="S417" t="inlineStr">
         <is>
-          <t>11-10-2021 08:30</t>
+          <t>2021-11-10 08:30:00</t>
         </is>
       </c>
       <c r="T417" t="n">
@@ -40632,7 +40632,7 @@
       </c>
       <c r="S418" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T418" t="n">
@@ -40727,7 +40727,7 @@
       </c>
       <c r="S419" t="inlineStr">
         <is>
-          <t>12-02-2021 08:30</t>
+          <t>2021-12-02 08:30:00</t>
         </is>
       </c>
       <c r="T419" t="n">
@@ -40822,7 +40822,7 @@
       </c>
       <c r="S420" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T420" t="n">
@@ -40917,7 +40917,7 @@
       </c>
       <c r="S421" t="inlineStr">
         <is>
-          <t>12-04-2021 08:30</t>
+          <t>2021-12-04 08:30:00</t>
         </is>
       </c>
       <c r="T421" t="n">
@@ -41012,7 +41012,7 @@
       </c>
       <c r="S422" t="inlineStr">
         <is>
-          <t>25-05-2021 08:30</t>
+          <t>2021-05-25 08:30:00</t>
         </is>
       </c>
       <c r="T422" t="n">
@@ -41107,7 +41107,7 @@
       </c>
       <c r="S423" t="inlineStr">
         <is>
-          <t>16-06-2021 08:30</t>
+          <t>2021-06-16 08:30:00</t>
         </is>
       </c>
       <c r="T423" t="n">
@@ -41202,7 +41202,7 @@
       </c>
       <c r="S424" t="inlineStr">
         <is>
-          <t>19-07-2021 08:30</t>
+          <t>2021-07-19 08:30:00</t>
         </is>
       </c>
       <c r="T424" t="n">
@@ -41297,7 +41297,7 @@
       </c>
       <c r="S425" t="inlineStr">
         <is>
-          <t>16-08-2021 08:30</t>
+          <t>2021-08-16 08:30:00</t>
         </is>
       </c>
       <c r="T425" t="n">
@@ -41392,7 +41392,7 @@
       </c>
       <c r="S426" t="inlineStr">
         <is>
-          <t>08-09-2021 08:30</t>
+          <t>2021-08-09 08:30:00</t>
         </is>
       </c>
       <c r="T426" t="n">
@@ -41487,7 +41487,7 @@
       </c>
       <c r="S427" t="inlineStr">
         <is>
-          <t>14-10-2021 08:30</t>
+          <t>2021-10-14 08:30:00</t>
         </is>
       </c>
       <c r="T427" t="n">
@@ -41582,7 +41582,7 @@
       </c>
       <c r="S428" t="inlineStr">
         <is>
-          <t>11-11-2021 08:30</t>
+          <t>2021-11-11 08:30:00</t>
         </is>
       </c>
       <c r="T428" t="n">
@@ -41677,7 +41677,7 @@
       </c>
       <c r="S429" t="inlineStr">
         <is>
-          <t>09-12-2021 08:30</t>
+          <t>2021-09-12 08:30:00</t>
         </is>
       </c>
       <c r="T429" t="n">
@@ -41772,7 +41772,7 @@
       </c>
       <c r="S430" t="inlineStr">
         <is>
-          <t>16-02-2021 08:30</t>
+          <t>2021-02-16 08:30:00</t>
         </is>
       </c>
       <c r="T430" t="inlineStr"/>
@@ -41865,7 +41865,7 @@
       </c>
       <c r="S431" t="inlineStr">
         <is>
-          <t>15-04-2021 08:30</t>
+          <t>2021-04-15 08:30:00</t>
         </is>
       </c>
       <c r="T431" t="n">
@@ -41964,7 +41964,7 @@
       </c>
       <c r="S432" t="inlineStr">
         <is>
-          <t>25-10-2021 08:30</t>
+          <t>2021-10-25 08:30:00</t>
         </is>
       </c>
       <c r="T432" t="n">
@@ -42063,7 +42063,7 @@
       </c>
       <c r="S433" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T433" t="n">
@@ -42162,7 +42162,7 @@
       </c>
       <c r="S434" t="inlineStr">
         <is>
-          <t>29-10-2021 08:30</t>
+          <t>2021-10-29 08:30:00</t>
         </is>
       </c>
       <c r="T434" t="n">
@@ -42261,7 +42261,7 @@
       </c>
       <c r="S435" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T435" t="n">
@@ -42360,7 +42360,7 @@
       </c>
       <c r="S436" t="inlineStr">
         <is>
-          <t>29-10-2021 08:30</t>
+          <t>2021-10-29 08:30:00</t>
         </is>
       </c>
       <c r="T436" t="n">
@@ -42459,7 +42459,7 @@
       </c>
       <c r="S437" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T437" t="n">
@@ -42558,7 +42558,7 @@
       </c>
       <c r="S438" t="inlineStr">
         <is>
-          <t>26-10-2021 08:30</t>
+          <t>2021-10-26 08:30:00</t>
         </is>
       </c>
       <c r="T438" t="n">
@@ -42657,7 +42657,7 @@
       </c>
       <c r="S439" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T439" t="n">
@@ -42756,7 +42756,7 @@
       </c>
       <c r="S440" t="inlineStr">
         <is>
-          <t>29-10-2021 08:30</t>
+          <t>2021-10-29 08:30:00</t>
         </is>
       </c>
       <c r="T440" t="n">
@@ -42855,7 +42855,7 @@
       </c>
       <c r="S441" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T441" t="n">
@@ -42954,7 +42954,7 @@
       </c>
       <c r="S442" t="inlineStr">
         <is>
-          <t>29-10-2021 08:30</t>
+          <t>2021-10-29 08:30:00</t>
         </is>
       </c>
       <c r="T442" t="n">
@@ -43053,7 +43053,7 @@
       </c>
       <c r="S443" t="inlineStr">
         <is>
-          <t>07-04-2021 08:30</t>
+          <t>2021-07-04 08:30:00</t>
         </is>
       </c>
       <c r="T443" t="n">
@@ -43152,7 +43152,7 @@
       </c>
       <c r="S444" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T444" t="n">
@@ -43251,7 +43251,7 @@
       </c>
       <c r="S445" t="inlineStr">
         <is>
-          <t>15-04-2021 08:30</t>
+          <t>2021-04-15 08:30:00</t>
         </is>
       </c>
       <c r="T445" t="n">
@@ -43350,7 +43350,7 @@
       </c>
       <c r="S446" t="inlineStr">
         <is>
-          <t>25-10-2021 08:30</t>
+          <t>2021-10-25 08:30:00</t>
         </is>
       </c>
       <c r="T446" t="n">
@@ -43449,7 +43449,7 @@
       </c>
       <c r="S447" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T447" t="n">
@@ -43548,7 +43548,7 @@
       </c>
       <c r="S448" t="inlineStr">
         <is>
-          <t>11-10-2021 08:30</t>
+          <t>2021-11-10 08:30:00</t>
         </is>
       </c>
       <c r="T448" t="n">
@@ -43647,7 +43647,7 @@
       </c>
       <c r="S449" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T449" t="n">
@@ -43746,7 +43746,7 @@
       </c>
       <c r="S450" t="inlineStr">
         <is>
-          <t>29-10-2021 08:30</t>
+          <t>2021-10-29 08:30:00</t>
         </is>
       </c>
       <c r="T450" t="n">
@@ -43845,7 +43845,7 @@
       </c>
       <c r="S451" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T451" t="n">
@@ -43944,7 +43944,7 @@
       </c>
       <c r="S452" t="inlineStr">
         <is>
-          <t>11-10-2021 08:30</t>
+          <t>2021-11-10 08:30:00</t>
         </is>
       </c>
       <c r="T452" t="n">
@@ -44043,7 +44043,7 @@
       </c>
       <c r="S453" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T453" t="n">
@@ -44142,7 +44142,7 @@
       </c>
       <c r="S454" t="inlineStr">
         <is>
-          <t>29-10-2021 08:30</t>
+          <t>2021-10-29 08:30:00</t>
         </is>
       </c>
       <c r="T454" t="n">
@@ -44241,7 +44241,7 @@
       </c>
       <c r="S455" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T455" t="n">
@@ -44340,7 +44340,7 @@
       </c>
       <c r="S456" t="inlineStr">
         <is>
-          <t>27-10-2021 08:30</t>
+          <t>2021-10-27 08:30:00</t>
         </is>
       </c>
       <c r="T456" t="n">
@@ -44439,7 +44439,7 @@
       </c>
       <c r="S457" t="inlineStr">
         <is>
-          <t>12-06-2021 08:30</t>
+          <t>2021-12-06 08:30:00</t>
         </is>
       </c>
       <c r="T457" t="n">
@@ -44538,7 +44538,7 @@
       </c>
       <c r="S458" t="inlineStr">
         <is>
-          <t>18-10-2021 08:30</t>
+          <t>2021-10-18 08:30:00</t>
         </is>
       </c>
       <c r="T458" t="n">
@@ -44637,7 +44637,7 @@
       </c>
       <c r="S459" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T459" t="n">
@@ -44736,7 +44736,7 @@
       </c>
       <c r="S460" t="inlineStr">
         <is>
-          <t>11-10-2021 08:30</t>
+          <t>2021-11-10 08:30:00</t>
         </is>
       </c>
       <c r="T460" t="n">
@@ -44835,7 +44835,7 @@
       </c>
       <c r="S461" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T461" t="n">
@@ -44934,7 +44934,7 @@
       </c>
       <c r="S462" t="inlineStr">
         <is>
-          <t>29-10-2021 08:30</t>
+          <t>2021-10-29 08:30:00</t>
         </is>
       </c>
       <c r="T462" t="n">
@@ -45033,7 +45033,7 @@
       </c>
       <c r="S463" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T463" t="n">
@@ -45132,7 +45132,7 @@
       </c>
       <c r="S464" t="inlineStr">
         <is>
-          <t>26-10-2021 08:30</t>
+          <t>2021-10-26 08:30:00</t>
         </is>
       </c>
       <c r="T464" t="n">
@@ -45231,7 +45231,7 @@
       </c>
       <c r="S465" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T465" t="n">
@@ -45330,7 +45330,7 @@
       </c>
       <c r="S466" t="inlineStr">
         <is>
-          <t>26-10-2021 08:30</t>
+          <t>2021-10-26 08:30:00</t>
         </is>
       </c>
       <c r="T466" t="n">
@@ -45429,7 +45429,7 @@
       </c>
       <c r="S467" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T467" t="n">
@@ -45528,7 +45528,7 @@
       </c>
       <c r="S468" t="inlineStr">
         <is>
-          <t>26-10-2021 08:30</t>
+          <t>2021-10-26 08:30:00</t>
         </is>
       </c>
       <c r="T468" t="n">
@@ -45627,7 +45627,7 @@
       </c>
       <c r="S469" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T469" t="n">
@@ -45726,7 +45726,7 @@
       </c>
       <c r="S470" t="inlineStr">
         <is>
-          <t>29-10-2021 08:30</t>
+          <t>2021-10-29 08:30:00</t>
         </is>
       </c>
       <c r="T470" t="n">
@@ -45825,7 +45825,7 @@
       </c>
       <c r="S471" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T471" t="n">
@@ -45924,7 +45924,7 @@
       </c>
       <c r="S472" t="inlineStr">
         <is>
-          <t>29-10-2021 08:30</t>
+          <t>2021-10-29 08:30:00</t>
         </is>
       </c>
       <c r="T472" t="n">
@@ -46023,7 +46023,7 @@
       </c>
       <c r="S473" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T473" t="n">
@@ -46122,7 +46122,7 @@
       </c>
       <c r="S474" t="inlineStr">
         <is>
-          <t>29-10-2021 08:30</t>
+          <t>2021-10-29 08:30:00</t>
         </is>
       </c>
       <c r="T474" t="n">
@@ -46221,7 +46221,7 @@
       </c>
       <c r="S475" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T475" t="n">
@@ -46320,7 +46320,7 @@
       </c>
       <c r="S476" t="inlineStr">
         <is>
-          <t>29-10-2021 08:30</t>
+          <t>2021-10-29 08:30:00</t>
         </is>
       </c>
       <c r="T476" t="n">
@@ -46419,7 +46419,7 @@
       </c>
       <c r="S477" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T477" t="n">
@@ -46518,7 +46518,7 @@
       </c>
       <c r="S478" t="inlineStr">
         <is>
-          <t>29-10-2021 08:30</t>
+          <t>2021-10-29 08:30:00</t>
         </is>
       </c>
       <c r="T478" t="n">
@@ -46617,7 +46617,7 @@
       </c>
       <c r="S479" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T479" t="n">
@@ -46716,7 +46716,7 @@
       </c>
       <c r="S480" t="inlineStr">
         <is>
-          <t>29-10-2021 08:30</t>
+          <t>2021-10-29 08:30:00</t>
         </is>
       </c>
       <c r="T480" t="n">
